--- a/data/trans_orig/IP74A4_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP74A4_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adulto según si ha resuelto las cuotas de seguros en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Adultos según si tienen resuelto el retraso en los pagos de las cuotas de seguros en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -765,7 +765,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2737</t>
+          <t>2430</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>59,63%</t>
+          <t>52,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -800,7 +800,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3269</t>
+          <t>3199</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>45,37%</t>
+          <t>44,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1851</t>
+          <t>2156</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>40,33%</t>
+          <t>46,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>3936</t>
+          <t>4006</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>54,63%</t>
+          <t>55,6%</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2737</t>
+          <t>2430</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>59,63%</t>
+          <t>52,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3269</t>
+          <t>3199</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>45,37%</t>
+          <t>44,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1851</t>
+          <t>2156</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>40,33%</t>
+          <t>46,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3936</t>
+          <t>4006</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>54,63%</t>
+          <t>55,6%</t>
         </is>
       </c>
     </row>
